--- a/AAII_Financials/Quarterly/ACN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ACN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>ACN</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44439</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44347</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44165</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44074</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43708</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43524</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43434</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43343</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43159</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43069</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42978</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42886</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42794</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42704</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18718100</v>
+      </c>
+      <c r="E8" s="3">
         <v>18044100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18742100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17596300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17727900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16659300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17689500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16405800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16466800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15799500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16224300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15985200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16564600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15814200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15747800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15423700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16158800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15046700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14965200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13419300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13263800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12088100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11762200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10835300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10991300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11141500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11359000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11055700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11099700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10454100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10605500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10504000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10695000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10067800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9884300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9640900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9356800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>8762200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9005600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>8965600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12583800</v>
+      </c>
+      <c r="E9" s="3">
         <v>12584700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12545000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11985300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11901200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11684300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11866700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11068400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10968400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10921000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10776400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10803600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11035500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10979400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10561700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10477600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10844100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10522700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10048400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8953100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8859400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8492900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7863900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7394700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7462600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7782300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7711200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7621000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7571400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7399800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7308100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14685400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14882700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7219400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>13822400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6754200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>6447200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>6258000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>6275600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>6310000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6134300</v>
+      </c>
+      <c r="E10" s="3">
         <v>5459400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6197100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5610900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5826700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4975000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5822800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5337500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5498500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4878500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5447900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5181600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5529100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4834800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5186100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4946100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5314700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4524000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4916800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4466200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4404400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3595200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3898300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3440600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3528700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3359200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3647800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3434700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3528300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3054300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3297400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-4181400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-4187700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2848400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-3938100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2886700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2909600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2504200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2730000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2655600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1246,11 +1260,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>817300</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1258,11 +1272,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>1150400</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1270,11 +1284,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3">
         <v>1298700</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,22 +1496,25 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>307500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>615300</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1502,38 +1522,38 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>105900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>77400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>115400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>139700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>472100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>93900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>244400</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>96300</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1550,8 +1570,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1565,8 +1585,8 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1574,8 +1594,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1583,71 +1603,74 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>501600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>12300</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-295200</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>307900</v>
+      </c>
+      <c r="E15" s="3">
         <v>314400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>296000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>497100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>292000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>286000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>293300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>307300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>271200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>254600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>244900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>295900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>259600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>265300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15542800</v>
+      </c>
+      <c r="E17" s="3">
         <v>15550500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15560900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14918100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14745100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14414600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14741100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14011100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13758500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13637700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13519800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13346800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13858400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13625200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13154700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13155500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13652000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12985100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12530900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11460600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11145100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10434600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9871500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9290600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9278600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9652600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9591700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9484200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9381700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9067500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8976500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9034300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9060100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8785100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8386100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8340500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8483100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7635900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>7673600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>7475100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3175300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2493500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3181200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2678200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2982800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2244700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2948500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2394700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2708300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2161800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2704600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2638400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2706200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2189000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2593100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2268200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2506800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2061600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2434300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1958700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2118700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1653500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1890700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1544700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1712700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1488900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1767300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1571500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1718000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1386600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1629000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1469700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1634900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1282700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1498200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1300400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>873700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1126300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1332000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1490500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E20" s="3">
         <v>51900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-53100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>26600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>43000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-32600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>39200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>35700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>293400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>36300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-17000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-27900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>117900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>105000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>252700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>29200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>38800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-16500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-34100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>2200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-27600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3453300</v>
+      </c>
+      <c r="E21" s="3">
         <v>2756100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3530400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3148700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3231800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2563300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3202600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2717300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2960700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2410800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2913700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2640900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2914500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2417900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3115100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2792700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3030900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2589900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2918200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2417100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2601700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2229100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2463900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2284300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2130400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1960200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2205600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1808400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1931000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1601500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1826700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1696900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1856800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1469300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1731500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1529000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1072500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1310300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1521600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1656300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E22" s="3">
         <v>63600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>65400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>66200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>67600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>64700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12100</v>
-      </c>
-      <c r="T22" s="3">
-        <v>11200</v>
       </c>
       <c r="U22" s="3">
         <v>11200</v>
       </c>
       <c r="V22" s="3">
+        <v>11200</v>
+      </c>
+      <c r="W22" s="3">
         <v>13000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>28700</v>
-      </c>
-      <c r="X22" s="3">
-        <v>8900</v>
       </c>
       <c r="Y22" s="3">
         <v>8900</v>
       </c>
       <c r="Z22" s="3">
+        <v>8900</v>
+      </c>
+      <c r="AA22" s="3">
         <v>14100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>4900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>3600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>4000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>3000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3149800</v>
+      </c>
+      <c r="E23" s="3">
         <v>2456700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2967700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2075200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2951100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2288800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2955200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2332600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2654400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2095700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2616700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1959100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2631700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1946900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2601600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2245000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2494600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2050500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2406100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1917800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2094000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1762400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1986900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1783400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1680800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1509600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1800600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1560800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1704300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1376300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1610500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1456600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1612600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1244800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1494100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1292000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>874400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1118500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1331100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1458900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>761900</v>
+      </c>
+      <c r="E24" s="3">
         <v>597300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>725800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>625400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>707200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>466300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>639100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>613900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>673000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>386500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>606700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>550900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>583300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>396200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>605300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>552600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>675300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>392900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>586400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>480400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>524400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>301000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>464800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>477900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>428100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>257500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>425500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>415200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>435700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>235500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>319200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>408200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>513500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>188500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>305600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>308800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>169600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>231300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>271400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>328100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2387900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1859400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2241900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1449800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2244000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1822400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2316200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1718700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1981300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1709200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2010000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1408200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2048300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1550700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1996300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1692400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1819300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1657500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1819700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1437400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1569600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1461500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1522100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1305400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1252600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1252100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1375200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1145500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1268600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1140700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1291300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1048400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1099100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1056300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1188500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>983200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>704800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>887200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1059700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1130800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2339000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1825200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2211600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1414000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2197500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1788100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2278900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1684300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1932200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1674900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1973400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1373000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2010000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1523600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1965000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1665100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1786100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1634900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1791000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1416200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1549400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1440900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1500300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1287900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1228200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1234700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1357000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1130400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1249500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1124400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1274700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1029500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1083900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1000400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1123700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>932500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>669500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>838800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1004500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1069200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3230,8 +3291,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3245,17 +3306,17 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-40900</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-136700</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-51900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>53100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-26600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-43000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>32600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-39200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-35700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-293400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>17000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>27900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-117900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-105000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-252700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>27000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-38800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>14000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>34100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2339000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1825200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2211600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1414000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2197500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1788100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2278900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1684300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1932200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1674900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1973400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1373000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2010000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1523600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1965000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1665100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1786100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1634900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1791000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1416200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1549400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1440900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1500300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1287900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1228200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1234700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1357000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1130400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1249500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1124400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1274700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1029500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>863700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1123700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>932500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>669500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>838800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1004500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1069200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2339000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1825200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2211600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1414000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2197500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1788100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2278900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1684300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1932200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1674900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1973400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1373000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2010000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1523600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1965000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1665100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1786100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1634900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1791000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1416200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1549400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1440900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1500300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1287900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1228200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1234700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1357000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1130400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1249500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1124400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1274700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1029500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>863700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1123700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>932500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>669500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>838800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1004500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1069200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44439</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44347</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44165</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44074</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43708</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43524</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43434</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43343</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43159</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43069</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42978</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42886</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42794</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42704</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,210 +4305,214 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10165200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9399200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9649400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11478700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9631600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8490400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8306100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5004500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5537200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5121100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7140800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9045000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8535400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6238800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5899700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7889800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6703600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5466100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5637100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8168200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10009400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9166600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8594000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8415300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6442300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5436500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5810500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6126900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4769200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4464900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4363800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5061400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3928800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3595100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3681700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4126900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3382200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3238900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4077100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4905600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E42" s="3">
         <v>6400</v>
-      </c>
-      <c r="E42" s="3">
-        <v>5900</v>
       </c>
       <c r="F42" s="3">
         <v>5900</v>
       </c>
       <c r="G42" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H42" s="3">
         <v>5800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4500</v>
-      </c>
-      <c r="M42" s="3">
-        <v>4600</v>
       </c>
       <c r="N42" s="3">
         <v>4600</v>
       </c>
       <c r="O42" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P42" s="3">
         <v>4500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>83100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>94300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>3300</v>
       </c>
       <c r="AD42" s="3">
         <v>3300</v>
@@ -4431,162 +4521,168 @@
         <v>3300</v>
       </c>
       <c r="AF42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AG42" s="3">
         <v>3100</v>
       </c>
       <c r="AH42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AI42" s="3">
         <v>3200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2600</v>
-      </c>
-      <c r="AN42" s="3">
-        <v>2500</v>
       </c>
       <c r="AO42" s="3">
         <v>2500</v>
       </c>
       <c r="AP42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AQ42" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16036000</v>
+      </c>
+      <c r="E43" s="3">
         <v>15737500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16006700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14985100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15100900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14281300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14574600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13664800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13199400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13080500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13241400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12227200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12582700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12499200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12610400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11776800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12219100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11590900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11120400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9728200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9473400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8725400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8547700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7846900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8345600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8517900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8577400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8095100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8134100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8151400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8023100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7496400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7446700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7511300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7458000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>6885300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>6741700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>6563900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>6469000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>6222400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,618 +4803,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2730800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2864200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2404700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2430900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2678200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2530900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2312500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2183100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2333900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2122700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2668800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2105100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2257500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2318800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2158300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1940300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2080800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2122100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1857200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1765800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1657600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1665200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1401200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1393200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1354700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1447200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1214900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1225400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1235000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1213900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1150400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1024600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>958100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1175200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1163500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1082200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1079200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>958700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>819800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>845300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28938300</v>
+      </c>
+      <c r="E46" s="3">
         <v>28007300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28066700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28900700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27416500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25307700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25198300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20857800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21075400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20328800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23055600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23381900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23380100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21061000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20672500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21610900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21007700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19185100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18621700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19666500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21144900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19560700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18626100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17749800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16146200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15405300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15606100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15450600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14141700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13833300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13540400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13585600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12336900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12284900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12303800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>12097300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>11205700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>10764000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>11368400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>11976200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>925300</v>
+      </c>
+      <c r="E47" s="3">
         <v>852200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>803000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>721300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>593500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>441700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>371500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>334700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>231300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>238900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>198100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>197400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>176300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>325300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>393100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>364800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>367200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>376300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>367300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>367900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>368000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>350600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>343400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>367800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>323700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>340800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>336800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>311300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>255000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>249800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>258300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>238600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>251000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>254300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>266500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>252500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>250400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>243300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>290800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>266800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4593500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4511700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4317300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4306700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4320700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4106200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4176900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4278500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4039000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4093900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4044100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4167500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4278300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4466900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4631200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4677700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4844100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4905700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4811100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4821600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4667900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4646500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4606900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4728900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4668000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4607100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4540900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1391200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1341500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1282800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1243300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1264000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1228900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1196200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1159000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1140600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1041000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>968400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>928900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>956500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27821800</v>
+      </c>
+      <c r="E49" s="3">
         <v>27129700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24953300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24947200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24393000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23564200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23609500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24024200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22592700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17947300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16236400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17646000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14461100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14190700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15820700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15064100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14320700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14271900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14341400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12836800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10361100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9960700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9208400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8739000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8366600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7606800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7129300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7046300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6922700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6514700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6219600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6070100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5963500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6015000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5770700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5712700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5253700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4797100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4560100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4119600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1489700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1623200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1634200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1522100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1558400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1417000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1380400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1307300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1175100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3657600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2882400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>738600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2808100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2707500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5598300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5545900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5555400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5578800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5533300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5483000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5583000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5466800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5483500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5493100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5552800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5543500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5557500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5590500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5495500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5509600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5444800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3290800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3470400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3382500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3474100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3486700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>3384700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3306000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>3295500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>3289900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68806600</v>
+      </c>
+      <c r="E54" s="3">
         <v>67064200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>64698500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>65394900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>63362000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>59869800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>59868100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>55932400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54141300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>51307500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>51531400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>51245300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>50128300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47727300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47115800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47263400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46095200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44317800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43674700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43175800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42124900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39985400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>38268300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37078600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35057300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33503400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33170700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29789900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28156400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>27390200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26706400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>24449100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23250800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23133000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>22974200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>22689900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>21135600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>20078800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>20443700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>20609000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,237 +6145,241 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3176700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3116700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2971600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2695600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2678900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2614900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2579200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2743800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2251300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2228400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2574700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2491200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2388500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2470900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2417800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2559500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2384400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2229200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2210200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2274100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1926900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1740400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1513400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1349900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1406000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1526100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1581100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1646600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1563000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1472100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1355500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1348800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1389000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1367500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1316900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1525100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1291100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1212800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1163300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1280800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>863700</v>
+      </c>
+      <c r="E58" s="3">
         <v>868800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>842900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>843500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>839300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>806300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>824300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1672400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2290500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>793700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>788400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>795200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>701000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>711400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>9100</v>
       </c>
       <c r="U58" s="3">
         <v>9100</v>
       </c>
       <c r="V58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="W58" s="3">
         <v>12100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3000</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>2900</v>
       </c>
       <c r="AM58" s="3">
         <v>2900</v>
@@ -6254,501 +6388,516 @@
         <v>2900</v>
       </c>
       <c r="AO58" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="AP58" s="3">
         <v>2800</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7251900</v>
+      </c>
+      <c r="E59" s="3">
         <v>7377000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6338300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6929000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6769700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6186700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5613900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5949200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5927400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5816400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5265100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5716600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5936000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5761500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14033000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14954800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14169500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13301800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13012800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13422700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12993500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12341200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11296700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11304900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10413600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9644700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9614600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9408800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8984900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8742600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8816100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8797600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8161800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7997500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8543100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8296300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7860200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7137000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>8004000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>7595300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21609100</v>
+      </c>
+      <c r="E60" s="3">
         <v>20957400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19896500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20352100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18768800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17130400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17187000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18976100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18207800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16136000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17280200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18009000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17092500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16349500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16460200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17523500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16562600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15540100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15232000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15708900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14929600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14090700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12819100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12662600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11828300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11177600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11199400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11061900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10552000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>10219000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>10176300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10151800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9553600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9367900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9863000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>9824300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>9154300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>8352800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>9170100</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>8878900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7525000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7478600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7359100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7339400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7325900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7254000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7322100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2448100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2311000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2364900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2291800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2353800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2395200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2497100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>45900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>51500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>52200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>55900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>53500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>61600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>59300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>59900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>54100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>60300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>19900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>19800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>19900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>19700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>25900</v>
-      </c>
-      <c r="AK61" s="3">
-        <v>22200</v>
       </c>
       <c r="AL61" s="3">
         <v>22200</v>
       </c>
       <c r="AM61" s="3">
+        <v>22200</v>
+      </c>
+      <c r="AN61" s="3">
         <v>24700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>24500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>24600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2664700</v>
+      </c>
+      <c r="E62" s="3">
         <v>2610400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2505600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2489700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2568200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2351300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2334700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2454100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2234900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2141200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1836600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1779000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1810100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1691000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6944500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6946900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7469300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7568600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7448200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7316400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7239700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6993000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6963100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6862800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6685100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6391900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6354200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3884000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3441600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3422900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3454600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3553100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3518500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3300700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3195500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3133200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3079900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3086300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3214900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3516200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35298800</v>
+      </c>
+      <c r="E66" s="3">
         <v>34289200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32776200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33153900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31812500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29687800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29765600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26764100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25521600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23351000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24045900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24786700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24066300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23270000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24141200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25157300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24706100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23757800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23321500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23646400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22782000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21677400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20361800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20078100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19042700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18028800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18003600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15380900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14419000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14053200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14027600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14084300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13453500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13450300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13872000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13740400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12968200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12114500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>13026600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>13053700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24026000</v>
+      </c>
+      <c r="E72" s="3">
         <v>22804000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22148100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21018700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26450200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25210000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24402600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23082400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22242200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21151600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20429400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19316200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18692100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17500000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16981400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18203800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17177400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16028400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15110700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13988700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15004300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14035800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13276700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12375500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12565900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11867500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11236300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10421500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11709300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11422000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10384100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7952400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8296800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8149100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7339200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>7081900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8844800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8953200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8113500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7880000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31890600</v>
+      </c>
+      <c r="E76" s="3">
         <v>31210700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30867500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31195400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30554700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29246100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>29190500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28288600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27744500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27122900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26676800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25692800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25332400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23762600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22974600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22106100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21389100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20560000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20353200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19529500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19342800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18308000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17906500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17000500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16014600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15474600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15167100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14409000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13737300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13337000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12678900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10364800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9797300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9682700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9102100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8949500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8167400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7964200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7417100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7555300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44439</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44347</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44165</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44074</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43708</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43524</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43434</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43343</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43159</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43069</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42978</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42886</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42794</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42704</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2339000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1825200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2211600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1414000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2197500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1788100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2278900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1684300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1932200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1674900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1973400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1373000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2010000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1523600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1965000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1665100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1786100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1634900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1791000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1416200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1549400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1440900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1500300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1287900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1228200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1234700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1357000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1130400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1249500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1124400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1274700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1029500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>863700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1123700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>932500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>669500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>838800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1004500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1069200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E83" s="3">
         <v>133800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>133100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>141600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>138100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>135000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>133200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>173800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>157700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>145000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>144000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>152700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>153300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>506200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>534900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>524200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>528300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>486300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>479000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>457800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>468200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>486900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>444700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>442100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>399500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>240200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>221300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>219600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>211700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>235100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>238400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>220700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>232600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>232100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>194500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>187800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>187400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>193400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3786200</v>
+      </c>
+      <c r="E89" s="3">
         <v>3817600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1664100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3914100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3684400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2853400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1022500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3389400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3142000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2101000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>498600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3409400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3289400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2330100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>495400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3790100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3064700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2155500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>530900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2436400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2401200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2534700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1602800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3156100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2741500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1530600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>786900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2116300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2123500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1359700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1027500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2109300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1987500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>924100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1005800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1941900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1792600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>154700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1083900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2066000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-186200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-149700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-156600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-107900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-169100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-170800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-152200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-213600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-124100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-109800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-68900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-180300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-141500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-107500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-98800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-177100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-194600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-164700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-181700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-236300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-158200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-92500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-93100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-188700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-150000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-165400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-95100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-241300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-140300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-139800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-179400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-173600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-132900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-133400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-191100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-135800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-104400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-84600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-320100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1206600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1740900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-504900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-771300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-455600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-407300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-385500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1547200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2208200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-855400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1367100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-478300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-782100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1408600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-667000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-272500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1912600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2851300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-572700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-439400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-446400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-246300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-885000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-597300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-375900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-655200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-451700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-272900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-375000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-270000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-345700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-652400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-547700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-344200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-689600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-62500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>994400</v>
+      </c>
+      <c r="E96" s="3">
         <v>1006800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1008900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>920900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>923000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>928100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>924700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>807100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>810200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>811800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>809200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>705300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>707000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>707200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-704900</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-613100</v>
       </c>
       <c r="S96" s="3">
         <v>-613100</v>
       </c>
       <c r="T96" s="3">
+        <v>-613100</v>
+      </c>
+      <c r="U96" s="3">
         <v>-615900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-612500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-557300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-558500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-560400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-557400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-507300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-509600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-510600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-507700</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-930300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-931500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-853800</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-817200</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-782500</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-785100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1766100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2413400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2911100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1275100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2220000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2205000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2751700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2429000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-216900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1865700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1551900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1480300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-972800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1515300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1676900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1101400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1103400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2036700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1069500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1367800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1012400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1546700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-999500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1013500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-798100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1289300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-948200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-351000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1122100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-831900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1462200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-531600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1295200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-703200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1179000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-592600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1123600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-681300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1162800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-588100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>132300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-56700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-87100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>53900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-58000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-46800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-52400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-24900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-26600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-93800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-56800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-26600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-93800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-56800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-17300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-79900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-58500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>26700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>23900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>21700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>76800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-31700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>25000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-70200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-88600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>38200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>47700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>22000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>32600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-60000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>766100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-250200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1829300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1847100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1141200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>184400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3301600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-532700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>416100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2019700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1904200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>509600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2296700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>339100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1990100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1186300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1237500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-171000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2531100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1841200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>842800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>572600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>178700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1973100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1005800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-374100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-316300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1357700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>304300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>101100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1132500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>333800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-86600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-445100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>744700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>143300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-838200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-828600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1407700</v>
       </c>
     </row>
